--- a/data/trans_dic/IP16A01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,85; 75,37</t>
+          <t>43,28; 76,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,91; 79,24</t>
+          <t>38,17; 79,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 66,27</t>
+          <t>5,89; 65,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,84; 79,07</t>
+          <t>41,4; 79,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,72; 92,8</t>
+          <t>41,95; 92,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,03; 77,41</t>
+          <t>33,14; 77,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97,01; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,07; 74,37</t>
+          <t>47,97; 73,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,61; 79,23</t>
+          <t>48,17; 80,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,37; 63,38</t>
+          <t>23,03; 64,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>98,44; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,21; 75,53</t>
+          <t>60,14; 75,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,75; 69,09</t>
+          <t>51,9; 69,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,82; 81,15</t>
+          <t>47,31; 82,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>98,56; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,84; 68,89</t>
+          <t>52,72; 68,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,39; 64,31</t>
+          <t>47,28; 64,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,14; 68,43</t>
+          <t>50,33; 67,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>99,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,18; 70,18</t>
+          <t>57,83; 69,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,2; 64,9</t>
+          <t>51,43; 63,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,27; 73,94</t>
+          <t>53,0; 72,72</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94,7; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,86; 80,27</t>
+          <t>55,76; 80,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,65; 78,12</t>
+          <t>48,59; 76,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,59; 71,24</t>
+          <t>47,07; 71,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>96,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,2; 78,05</t>
+          <t>52,49; 77,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,89; 62,93</t>
+          <t>33,15; 64,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,02; 71,58</t>
+          <t>44,22; 71,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97,82; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,51; 76,58</t>
+          <t>58,77; 75,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,14; 66,53</t>
+          <t>45,57; 66,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,48; 67,98</t>
+          <t>48,51; 67,47</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>99,0; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,7; 73,37</t>
+          <t>60,42; 72,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,45; 68,0</t>
+          <t>54,28; 68,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,7; 76,03</t>
+          <t>47,96; 74,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,11; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,88; 68,32</t>
+          <t>56,39; 68,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,55; 62,83</t>
+          <t>47,95; 62,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,0; 66,52</t>
+          <t>51,99; 65,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>99,53; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,41; 69,13</t>
+          <t>60,25; 69,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,08; 63,13</t>
+          <t>53,5; 63,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,86; 68,42</t>
+          <t>52,52; 67,87</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22048</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9406</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11307</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6439</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8676</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>42305</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25403</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15845</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>13942</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9981; 17676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5989; 12401</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>896; 9924</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7495; 14436</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3686; 8156</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5192; 12146</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>19748; 30334</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11792; 19650</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>7115; 19839</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>80707</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59559</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50483</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74156</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61205</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>71508</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>168376</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>120764</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>98034</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>145664</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>52518; 66059</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43063; 58016</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>57172; 100031</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>53260; 69447</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>40482; 54810</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>60404; 80902</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>108929; 131660</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>86706; 107295</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>127656; 175164</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>22551</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25033</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18324</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24596</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26435</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13990</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>27379</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>57816</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>51467</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>32313</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>51974</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20300; 29482</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13989; 22060</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19603; 29577</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20699; 30473</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9570; 18687</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>20565; 33204</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>44570; 57544</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26276; 38551</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>42760; 59474</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>125305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98686</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78212</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>104018</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>107562</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>268498</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197633</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>146191</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>211579</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>88690; 107012</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69181; 87247</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>85233; 133075</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>89414; 109213</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>59106; 77262</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>94726; 119965</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>183996; 211302</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>134154; 158441</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>189045; 244269</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Estudios-trans_dic.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,28; 76,65</t>
+          <t>44,13; 75,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,17; 79,03</t>
+          <t>37,45; 79,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 65,16</t>
+          <t>7,83; 66,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,4; 79,73</t>
+          <t>41,87; 79,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,95; 92,83</t>
+          <t>40,93; 92,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,14; 77,52</t>
+          <t>32,81; 79,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,97; 73,68</t>
+          <t>49,19; 72,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,17; 80,28</t>
+          <t>48,52; 79,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,03; 64,21</t>
+          <t>21,98; 63,37</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,14; 75,64</t>
+          <t>59,92; 75,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,9; 69,92</t>
+          <t>51,83; 68,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,31; 82,78</t>
+          <t>47,04; 80,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,72; 68,74</t>
+          <t>52,4; 68,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,28; 64,02</t>
+          <t>46,75; 64,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,33; 67,4</t>
+          <t>50,15; 67,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57,83; 69,9</t>
+          <t>57,57; 68,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,43; 63,64</t>
+          <t>52,41; 63,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,0; 72,72</t>
+          <t>52,75; 74,7</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,76; 80,99</t>
+          <t>55,39; 79,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,59; 76,62</t>
+          <t>46,87; 77,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,07; 71,03</t>
+          <t>46,65; 70,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,49; 77,28</t>
+          <t>54,78; 79,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,15; 64,73</t>
+          <t>33,7; 64,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,22; 71,39</t>
+          <t>45,86; 71,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58,77; 75,88</t>
+          <t>57,54; 75,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,57; 66,86</t>
+          <t>43,94; 66,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,51; 67,47</t>
+          <t>49,15; 68,36</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,42; 72,9</t>
+          <t>61,17; 73,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,28; 68,45</t>
+          <t>53,74; 68,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,96; 74,88</t>
+          <t>48,28; 74,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,39; 68,87</t>
+          <t>56,07; 69,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,95; 62,67</t>
+          <t>47,78; 62,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,99; 65,84</t>
+          <t>52,18; 65,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,25; 69,2</t>
+          <t>59,66; 69,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,5; 63,19</t>
+          <t>52,85; 62,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,52; 67,87</t>
+          <t>53,2; 67,73</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9981; 17676</t>
+          <t>10176; 17499</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5989; 12401</t>
+          <t>5876; 12471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>896; 9924</t>
+          <t>1193; 10089</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7495; 14436</t>
+          <t>7582; 14443</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3686; 8156</t>
+          <t>3596; 8120</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5192; 12146</t>
+          <t>5140; 12476</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19748; 30334</t>
+          <t>20249; 29852</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11792; 19650</t>
+          <t>11876; 19352</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7115; 19839</t>
+          <t>6791; 19578</t>
         </is>
       </c>
     </row>
@@ -1717,17 +1717,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52518; 66059</t>
+          <t>52327; 66150</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43063; 58016</t>
+          <t>43009; 57028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57172; 100031</t>
+          <t>56844; 97759</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53260; 69447</t>
+          <t>52944; 69534</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40482; 54810</t>
+          <t>40023; 55179</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60404; 80902</t>
+          <t>60191; 80760</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108929; 131660</t>
+          <t>108438; 129895</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86706; 107295</t>
+          <t>88361; 107673</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>127656; 175164</t>
+          <t>127060; 179940</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20300; 29482</t>
+          <t>20163; 29043</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13989; 22060</t>
+          <t>13496; 22281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19603; 29577</t>
+          <t>19428; 29210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20699; 30473</t>
+          <t>21600; 31348</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9570; 18687</t>
+          <t>9729; 18515</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20565; 33204</t>
+          <t>21329; 33396</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44570; 57544</t>
+          <t>43632; 57493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26276; 38551</t>
+          <t>25339; 38124</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42760; 59474</t>
+          <t>43331; 60265</t>
         </is>
       </c>
     </row>
@@ -2133,17 +2133,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88690; 107012</t>
+          <t>89801; 108483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69181; 87247</t>
+          <t>68501; 86885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85233; 133075</t>
+          <t>85806; 131950</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89414; 109213</t>
+          <t>88910; 109578</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59106; 77262</t>
+          <t>58903; 76857</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94726; 119965</t>
+          <t>95069; 120047</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2173,17 +2173,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183996; 211302</t>
+          <t>182190; 210777</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>134154; 158441</t>
+          <t>132523; 157678</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>189045; 244269</t>
+          <t>191488; 243782</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,44 +654,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>62,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73,28%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>58,63%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>61,12%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>59,94%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>53,48%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55,38%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>61,7%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>56,51%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,13; 75,88</t>
+          <t>41,84; 79,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,45; 79,48</t>
+          <t>38,72; 92,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 66,24</t>
+          <t>34,53; 79,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,87; 79,76</t>
+          <t>43,85; 75,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,93; 92,42</t>
+          <t>37,91; 79,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,81; 79,63</t>
+          <t>27,67; 75,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,19; 72,51</t>
+          <t>48,07; 74,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,52; 79,06</t>
+          <t>47,61; 79,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,98; 63,37</t>
+          <t>39,15; 72,05</t>
         </is>
       </c>
     </row>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>55,54%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60,15%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>68,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>60,84%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>61,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>52,17%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>60,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>55,54%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59,58%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>64,11%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,92; 75,74</t>
+          <t>51,84; 68,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,83; 68,73</t>
+          <t>46,39; 64,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,04; 80,9</t>
+          <t>50,26; 69,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,4; 68,82</t>
+          <t>59,21; 75,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,75; 64,45</t>
+          <t>51,75; 69,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,15; 67,29</t>
+          <t>43,21; 61,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57,57; 68,96</t>
+          <t>58,18; 70,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,41; 63,86</t>
+          <t>52,2; 64,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,75; 74,7</t>
+          <t>49,93; 62,08</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>67,04%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>68,76%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>63,64%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59,06%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>60,2%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>48,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>58,86%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>67,87%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,39; 79,78</t>
+          <t>53,2; 78,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,87; 77,39</t>
+          <t>31,89; 62,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,65; 70,14</t>
+          <t>42,58; 71,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,78; 79,5</t>
+          <t>52,86; 80,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,7; 64,13</t>
+          <t>48,65; 78,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45,86; 71,8</t>
+          <t>46,42; 72,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57,54; 75,81</t>
+          <t>59,51; 76,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,94; 66,12</t>
+          <t>45,14; 66,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,15; 68,36</t>
+          <t>49,99; 68,13</t>
         </is>
       </c>
     </row>
@@ -1074,44 +1074,44 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>62,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>67,23%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>61,36%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>54,53%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>59,03%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>64,72%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,17; 73,9</t>
+          <t>55,88; 68,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,74; 68,17</t>
+          <t>47,55; 62,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,28; 74,25</t>
+          <t>53,33; 66,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,07; 69,1</t>
+          <t>60,7; 73,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,78; 62,35</t>
+          <t>53,45; 68,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,18; 65,89</t>
+          <t>47,2; 61,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,66; 69,02</t>
+          <t>60,41; 69,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,85; 62,89</t>
+          <t>53,08; 63,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,2; 67,73</t>
+          <t>52,4; 61,93</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11307</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6439</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>14095</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>9406</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5266</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11307</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6439</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>13393</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10176; 17499</t>
+          <t>7575; 14317</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5876; 12471</t>
+          <t>3402; 8153</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1193; 10089</t>
+          <t>4806; 11129</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7582; 14443</t>
+          <t>10112; 17380</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3596; 8120</t>
+          <t>5948; 12434</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5140; 12476</t>
+          <t>2707; 7365</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20249; 29852</t>
+          <t>19790; 30616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11876; 19352</t>
+          <t>11653; 19392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6791; 19578</t>
+          <t>9278; 17076</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61205</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64911</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>59559</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>50483</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74156</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61205</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47551</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71508</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>145664</t>
+          <t>113261</t>
         </is>
       </c>
     </row>
@@ -1717,17 +1717,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52327; 66150</t>
+          <t>52380; 69601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43009; 57028</t>
+          <t>39717; 55059</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56844; 97759</t>
+          <t>54239; 74597</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52944; 69534</t>
+          <t>51711; 65966</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40023; 55179</t>
+          <t>42939; 57327</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60191; 80760</t>
+          <t>40049; 56935</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108438; 129895</t>
+          <t>109583; 132188</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88361; 107673</t>
+          <t>88000; 109424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>127060; 179940</t>
+          <t>100164; 124536</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26435</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13990</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25089</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>25033</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>18324</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24596</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26435</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13990</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27379</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>49486</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20163; 29043</t>
+          <t>20979; 30779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13496; 22281</t>
+          <t>9206; 18167</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19428; 29210</t>
+          <t>18358; 30917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21600; 31348</t>
+          <t>19244; 29220</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9729; 18515</t>
+          <t>14006; 22492</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21329; 33396</t>
+          <t>18812; 29260</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43632; 57493</t>
+          <t>45132; 58073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25339; 38124</t>
+          <t>26030; 38363</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43331; 60265</t>
+          <t>41817; 56985</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>98162</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>98686</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>78212</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>104018</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98947</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67979</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>176140</t>
         </is>
       </c>
     </row>
@@ -2133,17 +2133,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89801; 108483</t>
+          <t>88618; 108340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68501; 86885</t>
+          <t>58624; 77455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85806; 131950</t>
+          <t>87974; 110339</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88910; 109578</t>
+          <t>89108; 107709</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58903; 76857</t>
+          <t>68124; 86669</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95069; 120047</t>
+          <t>67490; 87349</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2173,17 +2173,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182190; 210777</t>
+          <t>184488; 211108</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132523; 157678</t>
+          <t>133087; 158295</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>191488; 243782</t>
+          <t>161358; 190697</t>
         </is>
       </c>
     </row>
